--- a/outputs/xlsx/ki-readiness-check-bewertungsraster.xlsx
+++ b/outputs/xlsx/ki-readiness-check-bewertungsraster.xlsx
@@ -233,6 +233,287 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="18"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Priorisierungs-Matrix: Automatisierbarkeit × Umsetzbarkeit (Größe = Score)</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <bubbleChart>
+        <varyColors val="0"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>Bewertung!$A$3</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="E08A1E"/>
+            </a:solidFill>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <xVal>
+            <numRef>
+              <f>'Bewertung'!$E$3</f>
+            </numRef>
+          </xVal>
+          <yVal>
+            <numRef>
+              <f>'Bewertung'!$F$3</f>
+            </numRef>
+          </yVal>
+          <bubbleSize>
+            <numRef>
+              <f>'Bewertung'!$G$3</f>
+            </numRef>
+          </bubbleSize>
+          <bubble3D val="0"/>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>Bewertung!$A$4</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="121110"/>
+            </a:solidFill>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <xVal>
+            <numRef>
+              <f>'Bewertung'!$E$4</f>
+            </numRef>
+          </xVal>
+          <yVal>
+            <numRef>
+              <f>'Bewertung'!$F$4</f>
+            </numRef>
+          </yVal>
+          <bubbleSize>
+            <numRef>
+              <f>'Bewertung'!$G$4</f>
+            </numRef>
+          </bubbleSize>
+          <bubble3D val="0"/>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>Bewertung!$A$5</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="8A6D3B"/>
+            </a:solidFill>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <xVal>
+            <numRef>
+              <f>'Bewertung'!$E$5</f>
+            </numRef>
+          </xVal>
+          <yVal>
+            <numRef>
+              <f>'Bewertung'!$F$5</f>
+            </numRef>
+          </yVal>
+          <bubbleSize>
+            <numRef>
+              <f>'Bewertung'!$G$5</f>
+            </numRef>
+          </bubbleSize>
+          <bubble3D val="0"/>
+        </ser>
+        <ser>
+          <idx val="3"/>
+          <order val="3"/>
+          <tx>
+            <strRef>
+              <f>Bewertung!$A$6</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="4A4640"/>
+            </a:solidFill>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <xVal>
+            <numRef>
+              <f>'Bewertung'!$E$6</f>
+            </numRef>
+          </xVal>
+          <yVal>
+            <numRef>
+              <f>'Bewertung'!$F$6</f>
+            </numRef>
+          </yVal>
+          <bubbleSize>
+            <numRef>
+              <f>'Bewertung'!$G$6</f>
+            </numRef>
+          </bubbleSize>
+          <bubble3D val="0"/>
+        </ser>
+        <ser>
+          <idx val="4"/>
+          <order val="4"/>
+          <tx>
+            <strRef>
+              <f>Bewertung!$A$7</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="BF7014"/>
+            </a:solidFill>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <xVal>
+            <numRef>
+              <f>'Bewertung'!$E$7</f>
+            </numRef>
+          </xVal>
+          <yVal>
+            <numRef>
+              <f>'Bewertung'!$F$7</f>
+            </numRef>
+          </yVal>
+          <bubbleSize>
+            <numRef>
+              <f>'Bewertung'!$G$7</f>
+            </numRef>
+          </bubbleSize>
+          <bubble3D val="0"/>
+        </ser>
+        <axId val="10"/>
+        <axId val="20"/>
+      </bubbleChart>
+      <valAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+          <max val="6"/>
+          <min val="0"/>
+        </scaling>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Automatisierbarkeit →</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="20"/>
+      </valAx>
+      <valAx>
+        <axId val="20"/>
+        <scaling>
+          <orientation val="minMax"/>
+          <max val="6"/>
+          <min val="0"/>
+        </scaling>
+        <axPos val="l"/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>Umsetzbarkeit →</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>10</col>
+      <colOff>0</colOff>
+      <row>2</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="7200000" cy="4320000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -524,7 +805,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:E29"/>
+  <dimension ref="B2:E32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -612,136 +893,152 @@
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="3" t="inlineStr">
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>5. Matrix-Grafik</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="48" customHeight="1">
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>Im Blatt 'Bewertung' rechts neben der Tabelle: automatisch generiertes Blasendiagramm (Automatisierbarkeit × Umsetzbarkeit, Blasengröße = Score). Aktualisiert sich live, sobald Punkte eingetragen werden — deckt die ersten 5 Zeilen ab (Methodik-Norm: 3-5 Prozesse pro Check). Bei zwei Prozessen mit identischen Punktzahlen liegen die Blasen exakt übereinander — das ist korrekt abgebildet, keine Anzeigefehler. Vorlage für PDF-Seite 4 (dort als eigene, CI-gestaltete Grafik neu gezeichnet, diese Version ist zum Arbeiten/Vorab-Check gedacht, nicht 1:1 fürs Kunden-PDF).</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="3" t="inlineStr">
         <is>
           <t>Bewertungstabelle (fix, gleich für jeden Kunden)</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="B21" s="6" t="inlineStr">
+    <row r="24">
+      <c r="B24" s="6" t="inlineStr">
         <is>
           <t>Kriterium</t>
         </is>
       </c>
-      <c r="C21" s="6" t="inlineStr">
+      <c r="C24" s="6" t="inlineStr">
         <is>
           <t>1 Punkt</t>
         </is>
       </c>
-      <c r="D21" s="6" t="inlineStr">
+      <c r="D24" s="6" t="inlineStr">
         <is>
           <t>3 Punkte</t>
         </is>
       </c>
-      <c r="E21" s="6" t="inlineStr">
+      <c r="E24" s="6" t="inlineStr">
         <is>
           <t>5 Punkte</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="60" customHeight="1">
-      <c r="B22" s="7" t="inlineStr">
+    <row r="25" ht="60" customHeight="1">
+      <c r="B25" s="7" t="inlineStr">
         <is>
           <t>Zeitaufwand
 (Impact)</t>
         </is>
       </c>
-      <c r="C22" s="7" t="inlineStr">
+      <c r="C25" s="7" t="inlineStr">
         <is>
           <t>&lt; 2 Std./Monat gesamt</t>
         </is>
       </c>
-      <c r="D22" s="7" t="inlineStr">
+      <c r="D25" s="7" t="inlineStr">
         <is>
           <t>2–15 Std./Monat gesamt</t>
         </is>
       </c>
-      <c r="E22" s="7" t="inlineStr">
+      <c r="E25" s="7" t="inlineStr">
         <is>
           <t>&gt; 15 Std./Monat gesamt</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="60" customHeight="1">
-      <c r="B23" s="7" t="inlineStr">
+    <row r="26" ht="60" customHeight="1">
+      <c r="B26" s="7" t="inlineStr">
         <is>
           <t>Automatisierbarkeit</t>
         </is>
       </c>
-      <c r="C23" s="7" t="inlineStr">
+      <c r="C26" s="7" t="inlineStr">
         <is>
           <t>Stark individuell, viele
 Ausnahmen, Bauchentscheidung</t>
         </is>
       </c>
-      <c r="D23" s="7" t="inlineStr">
+      <c r="D26" s="7" t="inlineStr">
         <is>
           <t>Teilweise regelbasiert,
 einige Ausnahmen</t>
         </is>
       </c>
-      <c r="E23" s="7" t="inlineStr">
+      <c r="E26" s="7" t="inlineStr">
         <is>
           <t>Klar regelbasiert / strukturierte
 Eingabe-Ausgabe, wenig Ausnahmen</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="60" customHeight="1">
-      <c r="B24" s="7" t="inlineStr">
+    <row r="27" ht="60" customHeight="1">
+      <c r="B27" s="7" t="inlineStr">
         <is>
           <t>Umsetzbarkeit
 (Aufwand)</t>
         </is>
       </c>
-      <c r="C24" s="7" t="inlineStr">
+      <c r="C27" s="7" t="inlineStr">
         <is>
           <t>Tiefe Systemintegration,
 Change-Management, mehrere
 Abteilungen</t>
         </is>
       </c>
-      <c r="D24" s="7" t="inlineStr">
+      <c r="D27" s="7" t="inlineStr">
         <is>
           <t>Ein System, moderate
 Einrichtung, ein Verantwortlicher</t>
         </is>
       </c>
-      <c r="E24" s="7" t="inlineStr">
+      <c r="E27" s="7" t="inlineStr">
         <is>
           <t>Steht-Tool oder einfacher
 Workflow, in Tagen umsetzbar</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="B26" s="4" t="inlineStr">
+    <row r="29">
+      <c r="B29" s="4" t="inlineStr">
         <is>
           <t>Score = Zeitaufwand × Automatisierbarkeit × Umsetzbarkeit (Produkt, 1–125)</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="B27" s="8" t="inlineStr">
+    <row r="30">
+      <c r="B30" s="8" t="inlineStr">
         <is>
           <t>Schwellen: ≥ 60 = Sofort · 20–59 = 3 Monate · &lt; 20 = Beobachten</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="B29" s="2" t="inlineStr">
+    <row r="32">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>Std./Woche → Std./Monat: × 4,33 (Umrechnungsfaktor, bereits in den Formeln hinterlegt)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="10">
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="B16:C16"/>
     <mergeCell ref="B7:C7"/>
     <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B20:C20"/>
     <mergeCell ref="B10:C10"/>
     <mergeCell ref="B14:C14"/>
     <mergeCell ref="B17:C17"/>
@@ -1082,11 +1379,11 @@
     </row>
     <row r="3" ht="20" customHeight="1">
       <c r="A3" s="10">
-        <f>Prozesse!A3</f>
+        <f>IF(Prozesse!A3="","",Prozesse!A3)</f>
         <v/>
       </c>
       <c r="B3" s="11">
-        <f>Prozesse!F3</f>
+        <f>IF(Prozesse!F3="","",Prozesse!F3)</f>
         <v/>
       </c>
       <c r="C3" s="11">
@@ -1111,11 +1408,11 @@
     </row>
     <row r="4" ht="20" customHeight="1">
       <c r="A4" s="10">
-        <f>Prozesse!A4</f>
+        <f>IF(Prozesse!A4="","",Prozesse!A4)</f>
         <v/>
       </c>
       <c r="B4" s="11">
-        <f>Prozesse!F4</f>
+        <f>IF(Prozesse!F4="","",Prozesse!F4)</f>
         <v/>
       </c>
       <c r="C4" s="11">
@@ -1140,11 +1437,11 @@
     </row>
     <row r="5" ht="20" customHeight="1">
       <c r="A5" s="10">
-        <f>Prozesse!A5</f>
+        <f>IF(Prozesse!A5="","",Prozesse!A5)</f>
         <v/>
       </c>
       <c r="B5" s="11">
-        <f>Prozesse!F5</f>
+        <f>IF(Prozesse!F5="","",Prozesse!F5)</f>
         <v/>
       </c>
       <c r="C5" s="11">
@@ -1169,11 +1466,11 @@
     </row>
     <row r="6" ht="20" customHeight="1">
       <c r="A6" s="10">
-        <f>Prozesse!A6</f>
+        <f>IF(Prozesse!A6="","",Prozesse!A6)</f>
         <v/>
       </c>
       <c r="B6" s="11">
-        <f>Prozesse!F6</f>
+        <f>IF(Prozesse!F6="","",Prozesse!F6)</f>
         <v/>
       </c>
       <c r="C6" s="11">
@@ -1198,11 +1495,11 @@
     </row>
     <row r="7" ht="20" customHeight="1">
       <c r="A7" s="10">
-        <f>Prozesse!A7</f>
+        <f>IF(Prozesse!A7="","",Prozesse!A7)</f>
         <v/>
       </c>
       <c r="B7" s="11">
-        <f>Prozesse!F7</f>
+        <f>IF(Prozesse!F7="","",Prozesse!F7)</f>
         <v/>
       </c>
       <c r="C7" s="11">
@@ -1227,11 +1524,11 @@
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="10">
-        <f>Prozesse!A8</f>
+        <f>IF(Prozesse!A8="","",Prozesse!A8)</f>
         <v/>
       </c>
       <c r="B8" s="11">
-        <f>Prozesse!F8</f>
+        <f>IF(Prozesse!F8="","",Prozesse!F8)</f>
         <v/>
       </c>
       <c r="C8" s="11">
@@ -1256,11 +1553,11 @@
     </row>
     <row r="9" ht="20" customHeight="1">
       <c r="A9" s="10">
-        <f>Prozesse!A9</f>
+        <f>IF(Prozesse!A9="","",Prozesse!A9)</f>
         <v/>
       </c>
       <c r="B9" s="11">
-        <f>Prozesse!F9</f>
+        <f>IF(Prozesse!F9="","",Prozesse!F9)</f>
         <v/>
       </c>
       <c r="C9" s="11">
@@ -1285,11 +1582,11 @@
     </row>
     <row r="10" ht="20" customHeight="1">
       <c r="A10" s="10">
-        <f>Prozesse!A10</f>
+        <f>IF(Prozesse!A10="","",Prozesse!A10)</f>
         <v/>
       </c>
       <c r="B10" s="11">
-        <f>Prozesse!F10</f>
+        <f>IF(Prozesse!F10="","",Prozesse!F10)</f>
         <v/>
       </c>
       <c r="C10" s="11">
@@ -1314,11 +1611,11 @@
     </row>
     <row r="11" ht="20" customHeight="1">
       <c r="A11" s="10">
-        <f>Prozesse!A11</f>
+        <f>IF(Prozesse!A11="","",Prozesse!A11)</f>
         <v/>
       </c>
       <c r="B11" s="11">
-        <f>Prozesse!F11</f>
+        <f>IF(Prozesse!F11="","",Prozesse!F11)</f>
         <v/>
       </c>
       <c r="C11" s="11">
@@ -1343,11 +1640,11 @@
     </row>
     <row r="12" ht="20" customHeight="1">
       <c r="A12" s="10">
-        <f>Prozesse!A12</f>
+        <f>IF(Prozesse!A12="","",Prozesse!A12)</f>
         <v/>
       </c>
       <c r="B12" s="11">
-        <f>Prozesse!F12</f>
+        <f>IF(Prozesse!F12="","",Prozesse!F12)</f>
         <v/>
       </c>
       <c r="C12" s="11">
@@ -1410,5 +1707,6 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
--- a/outputs/xlsx/ki-readiness-check-bewertungsraster.xlsx
+++ b/outputs/xlsx/ki-readiness-check-bewertungsraster.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Anleitung" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Prozesse" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Bewertung" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Anleitung" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prozesse" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Bewertung" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -236,19 +236,19 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="18"/>
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Priorisierungs-Matrix: Automatisierbarkeit × Umsetzbarkeit (Größe = Score)</a:t>
+              <a:t>Priorisierungs-Matrix: Zeitaufwand × Umsetzbarkeit (Größe = Score)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -266,16 +266,16 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="E08A1E"/>
             </a:solidFill>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <xVal>
             <numRef>
-              <f>'Bewertung'!$E$3</f>
+              <f>'Bewertung'!$D$3</f>
             </numRef>
           </xVal>
           <yVal>
@@ -299,16 +299,16 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="121110"/>
             </a:solidFill>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <xVal>
             <numRef>
-              <f>'Bewertung'!$E$4</f>
+              <f>'Bewertung'!$D$4</f>
             </numRef>
           </xVal>
           <yVal>
@@ -332,16 +332,16 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="8A6D3B"/>
             </a:solidFill>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <xVal>
             <numRef>
-              <f>'Bewertung'!$E$5</f>
+              <f>'Bewertung'!$D$5</f>
             </numRef>
           </xVal>
           <yVal>
@@ -365,16 +365,16 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="4A4640"/>
             </a:solidFill>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <xVal>
             <numRef>
-              <f>'Bewertung'!$E$6</f>
+              <f>'Bewertung'!$D$6</f>
             </numRef>
           </xVal>
           <yVal>
@@ -398,16 +398,16 @@
             </strRef>
           </tx>
           <spPr>
-            <a:solidFill>
+            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:srgbClr val="BF7014"/>
             </a:solidFill>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <xVal>
             <numRef>
-              <f>'Bewertung'!$E$7</f>
+              <f>'Bewertung'!$D$7</f>
             </numRef>
           </xVal>
           <yVal>
@@ -436,13 +436,13 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
-                  <a:t>Automatisierbarkeit →</a:t>
+                  <a:t>Zeitaufwand (Impact) →</a:t>
                 </a:r>
               </a:p>
             </rich>
@@ -463,8 +463,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -490,7 +490,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>10</col>
@@ -505,9 +505,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -902,7 +902,7 @@
     <row r="20" ht="48" customHeight="1">
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>Im Blatt 'Bewertung' rechts neben der Tabelle: automatisch generiertes Blasendiagramm (Automatisierbarkeit × Umsetzbarkeit, Blasengröße = Score). Aktualisiert sich live, sobald Punkte eingetragen werden — deckt die ersten 5 Zeilen ab (Methodik-Norm: 3-5 Prozesse pro Check). Bei zwei Prozessen mit identischen Punktzahlen liegen die Blasen exakt übereinander — das ist korrekt abgebildet, keine Anzeigefehler. Vorlage für PDF-Seite 4 (dort als eigene, CI-gestaltete Grafik neu gezeichnet, diese Version ist zum Arbeiten/Vorab-Check gedacht, nicht 1:1 fürs Kunden-PDF).</t>
+          <t>Im Blatt 'Bewertung' rechts neben der Tabelle: automatisch generiertes Blasendiagramm (Zeitaufwand × Umsetzbarkeit, Blasengröße = Score — dieselben Achsen wie in der Word-Vorlage S.4 vorgesehen). Aktualisiert sich live, sobald Punkte eingetragen werden — deckt die ersten 5 Zeilen ab (Methodik-Norm: 3-5 Prozesse pro Check). Bei zwei Prozessen mit identischen Punktzahlen liegen die Blasen exakt übereinander — das ist korrekt abgebildet, keine Anzeigefehler. Als Screenshot direkt in die Word-Vorlage S.4 einfügen — keine manuelle Neuzeichnung nötig, Achsen stimmen bereits überein.</t>
         </is>
       </c>
     </row>
@@ -1054,7 +1054,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:AC12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1067,12 +1067,33 @@
     <col width="24" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="34" customWidth="1" min="10" max="10"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rohdaten pro Prozess — trage entweder Spalte B direkt ein, oder nutze C+D+E als Rechenhilfe (Häufigkeit × Minuten, Einheit Woche/Monat wählen — Spalte F rechnet automatisch in Std./Woche um).</t>
+          <t>Rohdaten pro Prozess — trage entweder Spalte B direkt ein, oder nutze C+D+E als Rechenhilfe (Häufigkeit × Minuten, Einheit Woche/Monat wählen — Spalte F rechnet automatisch in Std./Woche um). Spalte K (Bereich): die max. 3 Bereiche aus dem Kickoff-Bogen, für die Übertragung ins Word-Deliverable.</t>
+        </is>
+      </c>
+      <c r="Y1" s="2" t="inlineStr">
+        <is>
+          <t>Bereiche dieses Kunden (aus Kickoff-Bogen, hier eintragen, max. 3):</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>[Bereich 1]</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>[Bereich 2]</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>[Bereich 3]</t>
         </is>
       </c>
     </row>
@@ -1130,6 +1151,12 @@
       <c r="J2" s="9" t="inlineStr">
         <is>
           <t>Was würde mit der Zeit passieren</t>
+        </is>
+      </c>
+      <c r="K2" s="9" t="inlineStr">
+        <is>
+          <t>Bereich
+(aus Kickoff-Bogen, max. 3)</t>
         </is>
       </c>
     </row>
@@ -1147,6 +1174,7 @@
       <c r="H3" s="7" t="n"/>
       <c r="I3" s="7" t="n"/>
       <c r="J3" s="7" t="n"/>
+      <c r="K3" s="7" t="n"/>
     </row>
     <row r="4" ht="34" customHeight="1">
       <c r="A4" s="7" t="n"/>
@@ -1162,6 +1190,7 @@
       <c r="H4" s="7" t="n"/>
       <c r="I4" s="7" t="n"/>
       <c r="J4" s="7" t="n"/>
+      <c r="K4" s="7" t="n"/>
     </row>
     <row r="5" ht="34" customHeight="1">
       <c r="A5" s="7" t="n"/>
@@ -1177,6 +1206,7 @@
       <c r="H5" s="7" t="n"/>
       <c r="I5" s="7" t="n"/>
       <c r="J5" s="7" t="n"/>
+      <c r="K5" s="7" t="n"/>
     </row>
     <row r="6" ht="34" customHeight="1">
       <c r="A6" s="7" t="n"/>
@@ -1192,6 +1222,7 @@
       <c r="H6" s="7" t="n"/>
       <c r="I6" s="7" t="n"/>
       <c r="J6" s="7" t="n"/>
+      <c r="K6" s="7" t="n"/>
     </row>
     <row r="7" ht="34" customHeight="1">
       <c r="A7" s="7" t="n"/>
@@ -1207,6 +1238,7 @@
       <c r="H7" s="7" t="n"/>
       <c r="I7" s="7" t="n"/>
       <c r="J7" s="7" t="n"/>
+      <c r="K7" s="7" t="n"/>
     </row>
     <row r="8" ht="34" customHeight="1">
       <c r="A8" s="7" t="n"/>
@@ -1222,6 +1254,7 @@
       <c r="H8" s="7" t="n"/>
       <c r="I8" s="7" t="n"/>
       <c r="J8" s="7" t="n"/>
+      <c r="K8" s="7" t="n"/>
     </row>
     <row r="9" ht="34" customHeight="1">
       <c r="A9" s="7" t="n"/>
@@ -1237,6 +1270,7 @@
       <c r="H9" s="7" t="n"/>
       <c r="I9" s="7" t="n"/>
       <c r="J9" s="7" t="n"/>
+      <c r="K9" s="7" t="n"/>
     </row>
     <row r="10" ht="34" customHeight="1">
       <c r="A10" s="7" t="n"/>
@@ -1252,6 +1286,7 @@
       <c r="H10" s="7" t="n"/>
       <c r="I10" s="7" t="n"/>
       <c r="J10" s="7" t="n"/>
+      <c r="K10" s="7" t="n"/>
     </row>
     <row r="11" ht="34" customHeight="1">
       <c r="A11" s="7" t="n"/>
@@ -1267,6 +1302,7 @@
       <c r="H11" s="7" t="n"/>
       <c r="I11" s="7" t="n"/>
       <c r="J11" s="7" t="n"/>
+      <c r="K11" s="7" t="n"/>
     </row>
     <row r="12" ht="34" customHeight="1">
       <c r="A12" s="7" t="n"/>
@@ -1282,14 +1318,18 @@
       <c r="H12" s="7" t="n"/>
       <c r="I12" s="7" t="n"/>
       <c r="J12" s="7" t="n"/>
+      <c r="K12" s="7" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A1:K1"/>
   </mergeCells>
-  <dataValidations count="1">
+  <dataValidations count="2">
     <dataValidation sqref="D3 D4 D5 D6 D7 D8 D9 D10 D11 D12" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Woche,Monat"</formula1>
+    </dataValidation>
+    <dataValidation sqref="K3 K4 K5 K6 K7 K8 K9 K10 K11 K12" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>=$AA$1:$AC$1</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
